--- a/data/trans_orig/IP18A03-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP18A03-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>34478</t>
+          <t>34283</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>47676</t>
+          <t>47752</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>48,29%</t>
+          <t>48,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>66,78%</t>
+          <t>66,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>39050</t>
+          <t>39087</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>52572</t>
+          <t>52351</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>52,73%</t>
+          <t>52,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>70,99%</t>
+          <t>70,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>78443</t>
+          <t>77741</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>96307</t>
+          <t>97049</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>53,93%</t>
+          <t>53,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>66,21%</t>
+          <t>66,72%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23721</t>
+          <t>23645</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>36919</t>
+          <t>37114</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>51,71%</t>
+          <t>51,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21484</t>
+          <t>21705</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>35006</t>
+          <t>34969</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>47,27%</t>
+          <t>47,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>49146</t>
+          <t>48404</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>67010</t>
+          <t>67712</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>46,07%</t>
+          <t>46,55%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>233458</t>
+          <t>234446</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>262811</t>
+          <t>261389</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>62,7%</t>
+          <t>62,97%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>70,59%</t>
+          <t>70,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>257195</t>
+          <t>256968</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>285786</t>
+          <t>288236</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>62,84%</t>
+          <t>62,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>69,82%</t>
+          <t>70,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>501187</t>
+          <t>499713</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>540829</t>
+          <t>541269</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>64,12%</t>
+          <t>63,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>69,25%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>109515</t>
+          <t>110937</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>138868</t>
+          <t>137880</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>37,03%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>123525</t>
+          <t>121075</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>152116</t>
+          <t>152343</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>37,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>240808</t>
+          <t>240368</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>280450</t>
+          <t>281924</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>30,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>36,07%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>76280</t>
+          <t>75702</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>96463</t>
+          <t>96224</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>49,44%</t>
+          <t>49,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>62,52%</t>
+          <t>62,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>73331</t>
+          <t>73437</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>91984</t>
+          <t>91592</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>52,41%</t>
+          <t>52,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>65,74%</t>
+          <t>65,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>154820</t>
+          <t>155299</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>182822</t>
+          <t>181726</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>52,62%</t>
+          <t>52,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>61,77%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>57831</t>
+          <t>58070</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>78014</t>
+          <t>78592</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>37,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>50,56%</t>
+          <t>50,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>47937</t>
+          <t>48329</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>66590</t>
+          <t>66484</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>47,59%</t>
+          <t>47,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>111393</t>
+          <t>112489</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>139395</t>
+          <t>138916</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>38,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>47,38%</t>
+          <t>47,22%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>356422</t>
+          <t>357395</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>394946</t>
+          <t>395617</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>59,6%</t>
+          <t>59,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>66,04%</t>
+          <t>66,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>380792</t>
+          <t>381263</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>418133</t>
+          <t>419390</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>61,09%</t>
+          <t>61,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>67,09%</t>
+          <t>67,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>749907</t>
+          <t>749208</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>803198</t>
+          <t>804497</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>61,4%</t>
+          <t>61,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>65,77%</t>
+          <t>65,87%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>203072</t>
+          <t>202401</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>241596</t>
+          <t>240623</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>33,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>40,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>205155</t>
+          <t>203898</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>242496</t>
+          <t>242025</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>32,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>38,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>418108</t>
+          <t>416809</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>471399</t>
+          <t>472098</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>38,6%</t>
+          <t>38,66%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>45506</t>
+          <t>45759</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>60688</t>
+          <t>60578</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>52,61%</t>
+          <t>52,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>70,16%</t>
+          <t>70,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>39667</t>
+          <t>39979</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>54608</t>
+          <t>54038</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>51,17%</t>
+          <t>51,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>70,45%</t>
+          <t>69,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>88989</t>
+          <t>88727</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>110867</t>
+          <t>110516</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>54,26%</t>
+          <t>54,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>67,59%</t>
+          <t>67,38%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25816</t>
+          <t>25926</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>40998</t>
+          <t>40745</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>47,39%</t>
+          <t>47,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22906</t>
+          <t>23476</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>37847</t>
+          <t>37535</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>48,83%</t>
+          <t>48,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>53151</t>
+          <t>53502</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>75029</t>
+          <t>75291</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,74%</t>
+          <t>45,9%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>261782</t>
+          <t>262054</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>294640</t>
+          <t>293297</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>61,6%</t>
+          <t>61,67%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>69,34%</t>
+          <t>69,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>301301</t>
+          <t>301610</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>335114</t>
+          <t>335978</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>64,06%</t>
+          <t>64,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>71,24%</t>
+          <t>71,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>573536</t>
+          <t>574250</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>621369</t>
+          <t>621054</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>64,06%</t>
+          <t>64,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>69,4%</t>
+          <t>69,37%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>130307</t>
+          <t>131650</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>163165</t>
+          <t>162893</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>38,4%</t>
+          <t>38,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>135262</t>
+          <t>134398</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>169075</t>
+          <t>168766</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>35,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>273954</t>
+          <t>274269</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>321787</t>
+          <t>321073</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>35,86%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>94726</t>
+          <t>94039</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>113758</t>
+          <t>113770</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>60,5%</t>
+          <t>60,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>72,66%</t>
+          <t>72,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>92369</t>
+          <t>92600</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>111657</t>
+          <t>113348</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>56,43%</t>
+          <t>56,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>68,21%</t>
+          <t>69,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>191940</t>
+          <t>191683</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>220329</t>
+          <t>220331</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>59,93%</t>
+          <t>59,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>68,79%</t>
+          <t>68,8%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>42810</t>
+          <t>42798</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>61842</t>
+          <t>62529</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>39,5%</t>
+          <t>39,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>52045</t>
+          <t>50354</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>71333</t>
+          <t>71102</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>43,57%</t>
+          <t>43,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>99941</t>
+          <t>99939</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>128330</t>
+          <t>128587</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>40,07%</t>
+          <t>40,15%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>413497</t>
+          <t>415593</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>454263</t>
+          <t>454096</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>61,9%</t>
+          <t>62,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>68,0%</t>
+          <t>67,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>447643</t>
+          <t>445834</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>490076</t>
+          <t>488224</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>62,91%</t>
+          <t>62,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>68,87%</t>
+          <t>68,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>876940</t>
+          <t>873192</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>933441</t>
+          <t>934448</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>63,56%</t>
+          <t>63,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>67,66%</t>
+          <t>67,73%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>213756</t>
+          <t>213923</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>254522</t>
+          <t>252426</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>38,1%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>221515</t>
+          <t>223367</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>263948</t>
+          <t>265757</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>37,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>446169</t>
+          <t>445162</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>502670</t>
+          <t>506418</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>36,44%</t>
+          <t>36,71%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>32892</t>
+          <t>32774</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>44230</t>
+          <t>43915</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>58,58%</t>
+          <t>58,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>78,78%</t>
+          <t>78,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>40003</t>
+          <t>40061</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>51992</t>
+          <t>51941</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>63,26%</t>
+          <t>63,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>82,22%</t>
+          <t>82,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>76476</t>
+          <t>77036</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>92832</t>
+          <t>92985</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>64,06%</t>
+          <t>64,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>77,76%</t>
+          <t>77,89%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11917</t>
+          <t>12232</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23255</t>
+          <t>23373</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,42%</t>
+          <t>41,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11242</t>
+          <t>11293</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23231</t>
+          <t>23173</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>36,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>26548</t>
+          <t>26395</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>42904</t>
+          <t>42344</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>35,47%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>274364</t>
+          <t>273497</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>306689</t>
+          <t>306231</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>62,77%</t>
+          <t>62,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>70,17%</t>
+          <t>70,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>269613</t>
+          <t>266733</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>301676</t>
+          <t>301444</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>61,79%</t>
+          <t>61,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>69,13%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>551132</t>
+          <t>554198</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>596688</t>
+          <t>596427</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>63,1%</t>
+          <t>63,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>68,32%</t>
+          <t>68,29%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>130385</t>
+          <t>130843</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>162710</t>
+          <t>163577</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>37,23%</t>
+          <t>37,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>134686</t>
+          <t>134918</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>166749</t>
+          <t>169629</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>38,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>276748</t>
+          <t>277009</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>322304</t>
+          <t>319238</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>36,55%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>80775</t>
+          <t>81278</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>101468</t>
+          <t>101839</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>52,43%</t>
+          <t>52,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>65,86%</t>
+          <t>66,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>93351</t>
+          <t>93685</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>115721</t>
+          <t>115072</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>54,18%</t>
+          <t>54,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>67,16%</t>
+          <t>66,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>181906</t>
+          <t>180876</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>210447</t>
+          <t>210676</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>55,74%</t>
+          <t>55,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>64,48%</t>
+          <t>64,55%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>52588</t>
+          <t>52217</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>73281</t>
+          <t>72778</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>33,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>47,57%</t>
+          <t>47,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>56584</t>
+          <t>57233</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>78954</t>
+          <t>78620</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>33,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>45,82%</t>
+          <t>45,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>115914</t>
+          <t>115685</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>144455</t>
+          <t>145485</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>35,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,26%</t>
+          <t>44,58%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>401597</t>
+          <t>402102</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>440376</t>
+          <t>441011</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>62,04%</t>
+          <t>62,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>68,04%</t>
+          <t>68,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>415013</t>
+          <t>415971</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>455541</t>
+          <t>454660</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>61,77%</t>
+          <t>61,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>67,8%</t>
+          <t>67,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>827832</t>
+          <t>828723</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>884042</t>
+          <t>884751</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>62,75%</t>
+          <t>62,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>67,01%</t>
+          <t>67,07%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>206901</t>
+          <t>206266</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>245680</t>
+          <t>245175</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>216360</t>
+          <t>217241</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>256888</t>
+          <t>255930</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>435136</t>
+          <t>434427</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>491346</t>
+          <t>490455</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>37,18%</t>
         </is>
       </c>
     </row>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2989</t>
+          <t>2948</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>6200</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>45,68%</t>
+          <t>45,04%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5775</t>
+          <t>5157</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>61,21%</t>
+          <t>54,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10313</t>
+          <t>10595</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15195</t>
+          <t>15050</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>64,54%</t>
+          <t>66,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>94,18%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>345</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3556</t>
+          <t>3597</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>54,32%</t>
+          <t>54,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5695,7 +5695,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3659</t>
+          <t>4277</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5710,7 +5710,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,79%</t>
+          <t>45,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>784</t>
+          <t>929</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5666</t>
+          <t>5384</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>33,7%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>44459</t>
+          <t>43512</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>55649</t>
+          <t>55816</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>67,12%</t>
+          <t>65,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>84,01%</t>
+          <t>84,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>64817</t>
+          <t>64925</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>77471</t>
+          <t>78179</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>71,03%</t>
+          <t>71,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>85,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>114140</t>
+          <t>113600</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>130857</t>
+          <t>130754</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>72,48%</t>
+          <t>72,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>83,09%</t>
+          <t>83,03%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10589</t>
+          <t>10422</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>21779</t>
+          <t>22726</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13778</t>
+          <t>13070</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>26432</t>
+          <t>26324</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>26630</t>
+          <t>26733</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>43347</t>
+          <t>43887</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>27,87%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18099</t>
+          <t>18114</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24990</t>
+          <t>24950</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>65,74%</t>
+          <t>65,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19098</t>
+          <t>18835</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27404</t>
+          <t>26991</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>61,79%</t>
+          <t>60,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>87,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>40094</t>
+          <t>39512</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>50505</t>
+          <t>50723</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>68,61%</t>
+          <t>67,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>86,79%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2541</t>
+          <t>2581</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9432</t>
+          <t>9417</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3505</t>
+          <t>3918</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11811</t>
+          <t>12074</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>39,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>7936</t>
+          <t>7718</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>18347</t>
+          <t>18929</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>32,39%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>69996</t>
+          <t>69339</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>84020</t>
+          <t>83614</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>69,78%</t>
+          <t>69,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>83,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>96721</t>
+          <t>97109</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>111564</t>
+          <t>111974</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>73,5%</t>
+          <t>73,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>85,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>170762</t>
+          <t>170971</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>191593</t>
+          <t>192659</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>73,63%</t>
+          <t>73,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>83,08%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>16294</t>
+          <t>16700</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>30318</t>
+          <t>30975</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>20028</t>
+          <t>19618</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>34871</t>
+          <t>34483</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>40313</t>
+          <t>39247</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>61144</t>
+          <t>60935</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,28%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP18A03-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP18A03-Estudios-trans_orig.xlsx
@@ -538,13 +538,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según su última visita al médico fue por diagnóstico y tratamiento en 2007 (tasa de respuesta: 99,78%)</t>
+          <t>Menores según si su última consulta médica fue por diagnóstico y/o tratamiento [en 2023 se preguntan por separado] en 2007 (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>46001</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>38938</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>52411</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>62,12%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>52,58%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>70,77%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>41125</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>34283</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>47752</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>33688</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>47197</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>57,6%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>48,02%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>66,88%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>46001</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>39087</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>52351</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>62,12%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>52,78%</t>
+          <t>47,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>70,69%</t>
+          <t>66,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>77741</t>
+          <t>77875</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>97049</t>
+          <t>96661</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>53,45%</t>
+          <t>53,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>66,72%</t>
+          <t>66,45%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>28055</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>21645</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>35118</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>37,88%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>29,23%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>47,42%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>30272</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>23645</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>37114</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>24200</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>37709</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>42,4%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>33,12%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>51,98%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>28055</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>21705</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>34969</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>37,88%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>47,22%</t>
+          <t>52,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>48404</t>
+          <t>48792</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>67712</t>
+          <t>67578</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>33,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>46,55%</t>
+          <t>46,46%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>74056</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>74056</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>74056</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>106</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>71397</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>71397</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>71397</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>74056</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>74056</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>74056</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>410</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>272851</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>258686</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>288220</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>66,66%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>63,2%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>70,42%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>373</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>248760</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>234446</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>261389</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>232799</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>262542</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>66,81%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>62,97%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>70,2%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>410</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>272851</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>256968</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>288236</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>66,66%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>62,78%</t>
+          <t>62,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>70,42%</t>
+          <t>70,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>499713</t>
+          <t>498747</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>541269</t>
+          <t>542655</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>63,93%</t>
+          <t>63,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>69,25%</t>
+          <t>69,43%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>136460</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>121091</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>150625</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>33,34%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>29,58%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>36,8%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>188</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>123566</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>110937</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>137880</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>109784</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>139527</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>33,19%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>29,8%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>37,03%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>136460</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>121075</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>152343</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>33,34%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>37,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>240368</t>
+          <t>238982</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>281924</t>
+          <t>282890</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>36,19%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>618</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>409311</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>409311</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>409311</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>561</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>372326</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>372326</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>372326</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>618</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>409311</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>409311</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>409311</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1414,67 +1414,67 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>82750</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>72067</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>91644</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>59,14%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>51,51%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>65,5%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>85702</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>75702</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>96224</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>75269</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>95236</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>55,54%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>49,06%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>62,36%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>82750</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>73437</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>91592</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>59,14%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>52,48%</t>
+          <t>48,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>65,46%</t>
+          <t>61,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>155299</t>
+          <t>155552</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>181726</t>
+          <t>181404</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>52,78%</t>
+          <t>52,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>61,77%</t>
+          <t>61,66%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>57171</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>48277</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>67854</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>40,86%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>34,5%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>48,49%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>101</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>68592</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>58070</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>78592</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>59058</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>79025</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>44,46%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>37,64%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>50,94%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>57171</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>48329</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>66484</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>40,86%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>38,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>47,52%</t>
+          <t>51,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>112489</t>
+          <t>112811</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>138916</t>
+          <t>138663</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>38,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>47,22%</t>
+          <t>47,13%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>139921</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>139921</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>139921</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>225</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>154294</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>154294</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>154294</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>139921</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>139921</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>139921</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>603</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>401602</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>382608</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>420603</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>64,43%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>61,39%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>67,48%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>557</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>375587</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>357395</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>395617</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>355869</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>393637</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>62,81%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>59,76%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>66,15%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>603</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>401602</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>381263</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>419390</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>64,43%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>61,17%</t>
+          <t>59,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>67,29%</t>
+          <t>65,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>749208</t>
+          <t>749860</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>804497</t>
+          <t>802559</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>61,34%</t>
+          <t>61,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>65,87%</t>
+          <t>65,71%</t>
         </is>
       </c>
     </row>
@@ -1870,67 +1870,67 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>221686</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>202685</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>240680</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>35,57%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>32,52%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>38,61%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>335</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
           <t>222431</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>202401</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>240623</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>204381</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>242149</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>37,19%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>33,85%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>40,24%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>335</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>221686</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>203898</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>242025</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>35,57%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>38,83%</t>
+          <t>40,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>416809</t>
+          <t>418747</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>472098</t>
+          <t>471446</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>34,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>38,6%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>938</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>623288</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>623288</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>623288</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>892</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>598018</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>598018</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>598018</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>938</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>623288</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>623288</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>623288</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2141,13 +2141,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según su última visita al médico fue por diagnóstico y tratamiento en 2012 (tasa de respuesta: 98,75%)</t>
+          <t>Menores según si su última consulta médica fue por diagnóstico y/o tratamiento [en 2023 se preguntan por separado] en 2012 (tasa de respuesta: 98,75%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2158,7 +2158,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2326,72 +2326,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>47093</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>39281</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>53946</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>60,75%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>50,68%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>69,6%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>78</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>53703</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>45759</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>60578</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>45782</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>60801</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>62,08%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>52,9%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>70,03%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>47093</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>39979</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>54038</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>60,75%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>51,58%</t>
+          <t>52,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>69,71%</t>
+          <t>70,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>88727</t>
+          <t>89605</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>110516</t>
+          <t>110956</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>54,1%</t>
+          <t>54,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>67,38%</t>
+          <t>67,65%</t>
         </is>
       </c>
     </row>
@@ -2439,72 +2439,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>30421</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>23568</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>38233</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>39,25%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>30,4%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>49,32%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>32801</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>25926</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>40745</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>25703</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>40722</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>37,92%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>29,97%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>47,1%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>30421</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>23476</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>37535</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>39,25%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>48,42%</t>
+          <t>47,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>53502</t>
+          <t>53062</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>75291</t>
+          <t>74413</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>32,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,9%</t>
+          <t>45,37%</t>
         </is>
       </c>
     </row>
@@ -2552,57 +2552,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>77514</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>77514</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>77514</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>125</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>86504</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>86504</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>86504</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>77514</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>77514</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>77514</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2669,72 +2669,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>459</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>319244</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>301591</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>335071</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>67,87%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>64,12%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>71,23%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>403</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>277931</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>262054</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>293297</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>260768</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>294602</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>65,4%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>61,67%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>69,02%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>459</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>319244</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>301610</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>335978</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>67,87%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>64,12%</t>
+          <t>61,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>71,43%</t>
+          <t>69,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>574250</t>
+          <t>574330</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>621054</t>
+          <t>622169</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>64,14%</t>
+          <t>64,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>69,37%</t>
+          <t>69,49%</t>
         </is>
       </c>
     </row>
@@ -2787,67 +2787,67 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>151132</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>135305</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>168785</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>32,13%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>28,77%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>35,88%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
           <t>147016</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>131650</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>162893</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>130345</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>164179</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>34,6%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>30,98%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>38,33%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>151132</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>134398</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>168766</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>32,13%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>38,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>274269</t>
+          <t>273154</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>321073</t>
+          <t>320993</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>35,85%</t>
         </is>
       </c>
     </row>
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>671</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>470376</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>470376</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>470376</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>615</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>424947</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>424947</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>424947</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>671</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>470376</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>470376</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>470376</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3012,72 +3012,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>102503</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>91612</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>112850</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>62,62%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>55,96%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>68,94%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>147</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>104044</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>94039</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>113770</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>94388</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>114632</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>66,45%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>60,06%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>72,67%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>102503</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>92600</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>113348</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>62,62%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>56,57%</t>
+          <t>60,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>69,24%</t>
+          <t>73,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>191683</t>
+          <t>193149</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>220331</t>
+          <t>221297</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>59,85%</t>
+          <t>60,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>68,8%</t>
+          <t>69,1%</t>
         </is>
       </c>
     </row>
@@ -3125,72 +3125,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>61199</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>50852</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>72090</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>37,38%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>31,06%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>44,04%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>74</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>52524</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>42798</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>62529</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>41936</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>62180</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>33,55%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>27,33%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>39,94%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>61199</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>50354</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>71102</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>37,38%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>43,43%</t>
+          <t>39,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>99939</t>
+          <t>98973</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>128587</t>
+          <t>127121</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>39,69%</t>
         </is>
       </c>
     </row>
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>163702</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>163702</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>163702</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>221</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>156568</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>156568</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>156568</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>163702</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>163702</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>163702</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3355,72 +3355,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>468840</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>448290</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>490476</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>65,89%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>63,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>68,93%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>628</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>435678</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>415593</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>454096</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>415703</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>455491</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>65,22%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>62,21%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>67,98%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>669</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>468840</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>445834</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>488224</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>65,89%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>62,65%</t>
+          <t>62,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>68,61%</t>
+          <t>68,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>873192</t>
+          <t>874302</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>934448</t>
+          <t>933363</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>63,29%</t>
+          <t>63,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>67,73%</t>
+          <t>67,65%</t>
         </is>
       </c>
     </row>
@@ -3468,72 +3468,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>342</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>242751</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>221115</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>263301</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>34,11%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>31,07%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>37,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>333</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>232341</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>213923</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>252426</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>212528</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>252316</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>34,78%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>32,02%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>37,79%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>342</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>242751</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>223367</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>265757</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>34,11%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>37,35%</t>
+          <t>37,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>445162</t>
+          <t>446247</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>506418</t>
+          <t>505308</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>32,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>36,63%</t>
         </is>
       </c>
     </row>
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1011</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>711591</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>711591</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>711591</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>961</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>668019</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>668019</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>668019</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1011</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>711591</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>711591</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>711591</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3744,13 +3744,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según su última visita al médico fue por diagnóstico y tratamiento en 2016 (tasa de respuesta: 98,83%)</t>
+          <t>Menores según si su última consulta médica fue por diagnóstico y/o tratamiento [en 2023 se preguntan por separado] en 2016 (tasa de respuesta: 98,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3761,7 +3761,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3929,72 +3929,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>46498</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>40396</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>51654</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>73,53%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>63,88%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>81,69%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>38658</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>32774</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>43915</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>32602</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>44264</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>68,85%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>58,37%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>78,21%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>46498</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>40061</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>51941</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>73,53%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>63,35%</t>
+          <t>58,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>82,14%</t>
+          <t>78,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>77036</t>
+          <t>76687</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>92985</t>
+          <t>93348</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>64,53%</t>
+          <t>64,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>78,19%</t>
         </is>
       </c>
     </row>
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>16736</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>11580</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>22838</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>26,47%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>18,31%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>36,12%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>17489</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>12232</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>23373</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>11883</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>23545</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>31,15%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>21,79%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>41,63%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>16736</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>11293</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>23173</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>26,47%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,65%</t>
+          <t>41,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>26395</t>
+          <t>26032</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>42344</t>
+          <t>42693</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>35,76%</t>
         </is>
       </c>
     </row>
@@ -4155,57 +4155,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>63234</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>63234</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>63234</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>84</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>56147</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>56147</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>56147</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>63234</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>63234</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>63234</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4272,72 +4272,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>403</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>284751</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>267278</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>299871</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>65,26%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>61,25%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>68,72%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>436</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>291038</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>273497</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>306231</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>273775</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>306675</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>66,59%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>62,57%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>70,06%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>403</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>284751</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>266733</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>301444</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>65,26%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>61,13%</t>
+          <t>62,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>69,08%</t>
+          <t>70,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>554198</t>
+          <t>551776</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>596427</t>
+          <t>598491</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>63,45%</t>
+          <t>63,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>68,29%</t>
+          <t>68,52%</t>
         </is>
       </c>
     </row>
@@ -4385,72 +4385,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>151611</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>136491</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>169084</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>34,74%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>31,28%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>38,75%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>225</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>146036</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>130843</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>163577</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>130399</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>163299</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>33,41%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>29,94%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>37,43%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>219</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>151611</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>134918</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>169629</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>34,74%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>38,87%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>277009</t>
+          <t>274945</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>319238</t>
+          <t>321660</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>36,83%</t>
         </is>
       </c>
     </row>
@@ -4498,57 +4498,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>622</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>436362</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>436362</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>436362</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>661</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>437074</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>437074</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>437074</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>622</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>436362</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>436362</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>436362</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4615,72 +4615,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>104743</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>93660</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>115712</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>60,79%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>54,36%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>67,16%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>136</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>91461</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>81278</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>101839</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>81760</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>101311</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>59,37%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>52,76%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>66,1%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>104743</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>93685</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>115072</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>60,79%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>54,37%</t>
+          <t>53,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>66,78%</t>
+          <t>65,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>180876</t>
+          <t>182690</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>210676</t>
+          <t>211262</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>55,42%</t>
+          <t>55,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>64,55%</t>
+          <t>64,73%</t>
         </is>
       </c>
     </row>
@@ -4728,72 +4728,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>67562</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>56593</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>78645</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>39,21%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>32,84%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>45,64%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>62595</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>52217</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>72778</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>52745</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>72296</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>40,63%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>33,9%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>47,24%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>67562</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>57233</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>78620</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>39,21%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>45,63%</t>
+          <t>46,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>115685</t>
+          <t>115099</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>145485</t>
+          <t>143671</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>35,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,58%</t>
+          <t>44,02%</t>
         </is>
       </c>
     </row>
@@ -4841,57 +4841,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>249</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>172305</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>172305</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>172305</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>154056</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>154056</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>154056</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>249</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>172305</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>172305</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>172305</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4958,72 +4958,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>620</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>435992</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>415725</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>456400</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>64,89%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>61,87%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>67,93%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>629</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>421157</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>402102</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>441011</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>401981</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>440299</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>65,07%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>62,12%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>68,13%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>620</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>435992</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>415971</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>454660</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>64,89%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>61,91%</t>
+          <t>62,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>67,67%</t>
+          <t>68,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>828723</t>
+          <t>829481</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>884751</t>
+          <t>885929</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>62,82%</t>
+          <t>62,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>67,16%</t>
         </is>
       </c>
     </row>
@@ -5071,72 +5071,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>341</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>235909</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>215501</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>256176</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>35,11%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>32,07%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>38,13%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>345</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>226120</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>206266</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>245175</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>206978</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>245296</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>34,93%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>31,87%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>37,88%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>341</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>235909</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>217241</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>255930</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>35,11%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>37,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>434427</t>
+          <t>433249</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>490455</t>
+          <t>489697</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>37,18%</t>
+          <t>37,12%</t>
         </is>
       </c>
     </row>
@@ -5184,57 +5184,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>961</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>671901</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>671901</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>671901</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>974</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>647277</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>647277</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>647277</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>961</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>671901</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>671901</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>671901</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5347,13 +5347,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según su última visita al médico fue por diagnóstico y tratamiento en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según si su última consulta médica fue por diagnóstico y/o tratamiento [en 2023 se preguntan por separado] en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5364,7 +5364,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5532,72 +5532,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>7903</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>5354</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>9091</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>86,93%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>58,9%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>5175</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2948</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6200</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>79,07%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>45,04%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>94,73%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>8161</t>
+          <t>4761</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5157</t>
+          <t>2873</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9434</t>
+          <t>5646</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>86,5%</t>
+          <t>79,96%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>54,67%</t>
+          <t>48,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>13336</t>
+          <t>12664</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10595</t>
+          <t>9637</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15050</t>
+          <t>14191</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>84,17%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>66,3%</t>
+          <t>64,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,32%</t>
         </is>
       </c>
     </row>
@@ -5645,72 +5645,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1188</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>3737</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>13,07%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>41,1%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>1370</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>345</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>3597</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>20,93%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>5,27%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>54,96%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>1193</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>308</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4277</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>45,33%</t>
+          <t>51,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>2643</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>929</t>
+          <t>855</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5384</t>
+          <t>5409</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>35,95%</t>
         </is>
       </c>
     </row>
@@ -5758,57 +5758,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>9091</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>9091</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>9091</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>6545</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>6545</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>6545</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>9434</t>
+          <t>5954</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9434</t>
+          <t>5954</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9434</t>
+          <t>5954</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>15979</t>
+          <t>15046</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>15979</t>
+          <t>15046</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>15979</t>
+          <t>15046</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5875,72 +5875,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>66404</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>59878</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>72124</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>79,23%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>71,45%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>86,06%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>74</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>50242</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>43512</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>55816</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>75,85%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>65,69%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>84,27%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>72289</t>
+          <t>46878</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>64925</t>
+          <t>40354</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>78179</t>
+          <t>52325</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>74,14%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>63,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>82,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>122531</t>
+          <t>113282</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>113600</t>
+          <t>104085</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>130754</t>
+          <t>120952</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>77,8%</t>
+          <t>77,05%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>72,13%</t>
+          <t>70,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>82,26%</t>
         </is>
       </c>
     </row>
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>17403</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>11683</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>23929</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>20,77%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>13,94%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>28,55%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>15996</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>10422</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>22726</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>24,15%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>15,73%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>34,31%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>18960</t>
+          <t>16348</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13070</t>
+          <t>10901</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>26324</t>
+          <t>22872</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>36,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>34956</t>
+          <t>33751</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>26733</t>
+          <t>26081</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>43887</t>
+          <t>42948</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>29,21%</t>
         </is>
       </c>
     </row>
@@ -6101,57 +6101,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>83807</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>83807</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>83807</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>98</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>66238</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>66238</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>66238</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>135</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>91249</t>
+          <t>63226</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>91249</t>
+          <t>63226</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>91249</t>
+          <t>63226</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>157487</t>
+          <t>147033</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>157487</t>
+          <t>147033</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>157487</t>
+          <t>147033</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6218,72 +6218,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>22136</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>17510</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>25665</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>76,8%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>60,75%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>89,04%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>21916</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>18114</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>24950</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>79,6%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>65,8%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>90,63%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>24143</t>
+          <t>20523</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18835</t>
+          <t>16328</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26991</t>
+          <t>23615</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>78,11%</t>
+          <t>77,94%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>60,94%</t>
+          <t>62,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>87,32%</t>
+          <t>89,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>46060</t>
+          <t>42659</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>39512</t>
+          <t>36374</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>50723</t>
+          <t>47153</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>78,81%</t>
+          <t>77,34%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>67,61%</t>
+          <t>65,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>86,79%</t>
+          <t>85,49%</t>
         </is>
       </c>
     </row>
@@ -6331,72 +6331,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>6688</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>3159</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>11314</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>23,2%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>10,96%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>39,25%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>5615</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>2581</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>9417</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>20,4%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>9,37%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>34,2%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6766</t>
+          <t>5809</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3918</t>
+          <t>2717</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12074</t>
+          <t>10004</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>37,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>12381</t>
+          <t>12496</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>7718</t>
+          <t>8002</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>18929</t>
+          <t>18781</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>34,05%</t>
         </is>
       </c>
     </row>
@@ -6444,57 +6444,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>28824</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>28824</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>28824</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>27531</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>27531</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>27531</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>30909</t>
+          <t>26332</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>30909</t>
+          <t>26332</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>30909</t>
+          <t>26332</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>58441</t>
+          <t>55155</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>58441</t>
+          <t>55155</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>58441</t>
+          <t>55155</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6561,72 +6561,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>96443</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>88848</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>103108</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>79,23%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>72,99%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>84,71%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>117</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>77333</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>69339</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>83614</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>77,09%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>69,12%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>83,35%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>104593</t>
+          <t>72162</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>97109</t>
+          <t>64389</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>111974</t>
+          <t>78663</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>79,48%</t>
+          <t>75,55%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>73,8%</t>
+          <t>67,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>85,09%</t>
+          <t>82,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>181926</t>
+          <t>168605</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>170971</t>
+          <t>157965</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>192659</t>
+          <t>178217</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>78,45%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>73,72%</t>
+          <t>72,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>82,04%</t>
         </is>
       </c>
     </row>
@@ -6674,72 +6674,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>25279</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>18614</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>32874</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>20,77%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>15,29%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>27,01%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>22981</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>16700</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>30975</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>22,91%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>16,65%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>30,88%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>26999</t>
+          <t>23350</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>19618</t>
+          <t>16849</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>34483</t>
+          <t>31123</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>49980</t>
+          <t>48629</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>39247</t>
+          <t>39017</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>60935</t>
+          <t>59269</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>27,28%</t>
         </is>
       </c>
     </row>
@@ -6787,57 +6787,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>121722</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>121722</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>121722</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>153</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>100314</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>100314</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>100314</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>131592</t>
+          <t>95512</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>131592</t>
+          <t>95512</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>131592</t>
+          <t>95512</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>231906</t>
+          <t>217234</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>231906</t>
+          <t>217234</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>231906</t>
+          <t>217234</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
